--- a/RaidenDemo/文档/配置表/EnemyResource.xlsx
+++ b/RaidenDemo/文档/配置表/EnemyResource.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R19747b5e22bb49ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc691c75d6bb943c0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -36,120 +36,111 @@
     <x:t xml:space="preserve">enemyClass</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">baseHealth</x:t>
+    <x:t xml:space="preserve">displaySize</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">fireInterval</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">fireType</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">bulletId</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">score</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">poolCapacity</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">aircraft</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">##</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">敌机ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">敌机类别</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">显示尺寸</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">开火间隔</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">射击模式</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">子弹ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">击毁分数</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">对象池容量</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">飞机实体</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">##type</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">int</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">EnemyClass</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">vector2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">float</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">EnemyFireType</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Aircraft</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">appearanceName</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">displaySize</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">hitSize</x:t>
+    <x:t xml:space="preserve">*collisionShapes</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">health</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">moveSpeed</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">fireInterval</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">fireType</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">bulletId</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">score</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">poolCapacity</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">aircraft</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">##</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">敌机ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">敌机类别</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">基础血量</x:t>
+    <x:t xml:space="preserve">bulletLaunchers</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">*deathExplosions</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">removeAfterDeathPresentation</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">外观资源名</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">显示尺寸</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">碰撞尺寸</x:t>
+    <x:t xml:space="preserve">碰撞形状列表</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">生命值</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">移动速度</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">开火间隔</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">射击模式</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">子弹ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">击毁分数</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">对象池容量</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">飞机实体</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">##type</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">int</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">EnemyClass</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">string</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">vector2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">float</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">EnemyFireType</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Aircraft</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">health</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">bulletLaunchers</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">*deathExplosions</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">removeAfterDeathPresentation</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">生命值</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">子弹发射器列表（待迁移）</x:t>
   </x:si>
   <x:si>
@@ -183,70 +174,76 @@
     <x:t xml:space="preserve">普通</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">99,150</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">单发</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">aircraft/enemy/battleEnemyScout</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">99,150</x:t>
+    <x:t xml:space="preserve">矩形</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">60,105</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">单发</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">矩形</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">0.5,0.5</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">0,0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">135,120</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">双发</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">aircraft/enemy/battleEnemyInterceptor</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">135,120</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">100,80</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">双发</x:t>
+    <x:t xml:space="preserve">140,130</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">散射</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">aircraft/enemy/battleEnemyBomber</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">140,130</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">110,90</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">散射</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">精英</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">193,180</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">aircraft/enemy/battleEliteInterceptor</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">193,180</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">150,130</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Boss</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">362,330</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">aircraft/enemy/battleBossStage01</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">362,330</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">290,250</x:t>
+    <x:t xml:space="preserve">90,180</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">105,90</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -260,25 +257,29 @@
     <x:numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <x:numFmt numFmtId="200" formatCode="@"/>
   </x:numFmts>
-  <x:fonts count="25">
+  <x:fonts count="26">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
-      <x:sz val="12"/>
+      <x:sz val="11"/>
       <x:color rgb="FFBDD7EE"/>
       <x:name val="微软雅黑"/>
     </x:font>
     <x:font>
-      <x:sz val="12"/>
+      <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="微软雅黑"/>
     </x:font>
     <x:font>
-      <x:sz val="12"/>
+      <x:sz val="11"/>
       <x:color rgb="FF000000"/>
       <x:name val="微软雅黑"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Microsoft YaHei"/>
     </x:font>
     <x:font>
       <x:sz val="11"/>
@@ -390,10 +391,11 @@
     </x:font>
     <x:font>
       <x:sz val="11"/>
-      <x:name val="Microsoft YaHei"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="36">
+  <x:fills count="37">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -570,8 +572,13 @@
         <x:fgColor theme="9" tint="0.39998"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="16">
+  <x:borders count="11">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -603,45 +610,16 @@
     </x:border>
     <x:border>
       <x:left style="thin">
-        <x:color rgb="FF7F7F7F"/>
+        <x:color rgb="FFD0D0D0"/>
       </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD0D0D0"/>
+      </x:right>
       <x:top style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:top style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:left>
-      <x:top style="thin">
-        <x:color rgb="FF7F7F7F"/>
+        <x:color rgb="FFD0D0D0"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:top style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF7F7F7F"/>
+        <x:color rgb="FFD0D0D0"/>
       </x:bottom>
     </x:border>
     <x:border>
@@ -709,250 +687,203 @@
         <x:color theme="4"/>
       </x:bottom>
     </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD0D0D0"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFD0D0D0"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFD0D0D0"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFD0D0D0"/>
-      </x:bottom>
-    </x:border>
   </x:borders>
   <x:cellStyleXfs count="50">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <x:xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="15" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="16" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <x:xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="49" fontId="24" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="24" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="36" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="36" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="36" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="25" fillId="36" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -1392,31 +1323,31 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="12" customWidth="1"/>
-    <x:col min="2" max="2" width="7.5" customWidth="1"/>
-    <x:col min="3" max="3" width="12.75" customWidth="1"/>
-    <x:col min="4" max="4" width="12.25" customWidth="1"/>
-    <x:col min="5" max="5" width="25.375" customWidth="1"/>
-    <x:col min="6" max="6" width="11.875" customWidth="1"/>
-    <x:col min="7" max="7" width="9.375" customWidth="1"/>
-    <x:col min="8" max="8" width="12.75" customWidth="1"/>
-    <x:col min="9" max="9" width="11.875" customWidth="1"/>
-    <x:col min="10" max="10" width="16.375" customWidth="1"/>
-    <x:col min="11" max="11" width="8.625" customWidth="1"/>
-    <x:col min="12" max="12" width="9.375" customWidth="1"/>
-    <x:col min="13" max="13" width="14.125" customWidth="1"/>
-    <x:col min="14" max="14" width="31" customWidth="1"/>
-    <x:col min="15" max="15" width="6.625" customWidth="1"/>
-    <x:col min="16" max="16" width="7.125" customWidth="1"/>
-    <x:col min="17" max="17" width="8.625" style="1" customWidth="1"/>
-    <x:col min="18" max="18" width="7.375" style="1" customWidth="1"/>
-    <x:col min="19" max="19" width="7.375" customWidth="1"/>
-    <x:col min="20" max="20" width="12.75" customWidth="1"/>
-    <x:col min="21" max="21" width="27.125" customWidth="1"/>
-    <x:col min="22" max="22" width="9.25" customWidth="1"/>
-    <x:col min="23" max="23" width="9" customWidth="1"/>
-    <x:col min="24" max="24" width="8.75" customWidth="1"/>
-    <x:col min="25" max="25" width="38.25" customWidth="1"/>
+    <x:col min="1" max="1" width="8" customWidth="1"/>
+    <x:col min="2" max="2" width="7" customWidth="1"/>
+    <x:col min="3" max="3" width="12.25" customWidth="1"/>
+    <x:col min="4" max="4" width="11.5" customWidth="1"/>
+    <x:col min="5" max="5" width="11.25" customWidth="1"/>
+    <x:col min="6" max="6" width="15.875" customWidth="1"/>
+    <x:col min="7" max="7" width="8.375" customWidth="1"/>
+    <x:col min="8" max="8" width="8.875" customWidth="1"/>
+    <x:col min="9" max="9" width="13.75" customWidth="1"/>
+    <x:col min="10" max="10" width="40.125" customWidth="1"/>
+    <x:col min="11" max="11" width="6.625" customWidth="1"/>
+    <x:col min="12" max="12" width="6.875" customWidth="1"/>
+    <x:col min="13" max="13" width="8.625" customWidth="1"/>
+    <x:col min="14" max="14" width="15" customWidth="1"/>
+    <x:col min="15" max="15" width="7" customWidth="1"/>
+    <x:col min="16" max="16" width="12.625" customWidth="1"/>
+    <x:col min="17" max="17" width="25.375" style="1" customWidth="1"/>
+    <x:col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <x:col min="19" max="19" width="8.875" customWidth="1"/>
+    <x:col min="20" max="20" width="8.375" customWidth="1"/>
+    <x:col min="21" max="21" width="35.875" customWidth="1"/>
+    <x:col min="22" max="22" width="28.5" customWidth="1"/>
+    <x:col min="23" max="23" width="8.383333206176758" customWidth="1"/>
+    <x:col min="24" max="24" width="7.883333206176758" customWidth="1"/>
+    <x:col min="25" max="25" width="28" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="20" customHeight="1">
@@ -1450,135 +1381,103 @@
       <x:c r="J1" s="2" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K1" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L1" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M1" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N1" s="5" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="O1" s="5"/>
-      <x:c r="P1" s="5"/>
-      <x:c r="Q1" s="5"/>
-      <x:c r="R1" s="5"/>
-      <x:c r="S1" s="5"/>
-      <x:c r="T1" s="5"/>
-      <x:c r="U1" s="5"/>
+      <x:c r="K1" s="2"/>
+      <x:c r="L1" s="2"/>
+      <x:c r="M1" s="2"/>
+      <x:c r="N1" s="2"/>
+      <x:c r="O1" s="2"/>
+      <x:c r="P1" s="2"/>
+      <x:c r="Q1" s="2"/>
+      <x:c r="R1" s="2"/>
+      <x:c r="S1" s="2"/>
+      <x:c r="T1" s="2"/>
+      <x:c r="U1" s="2"/>
     </x:row>
     <x:row r="2" ht="20" customHeight="1">
       <x:c r="A2" s="3" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B2" s="3" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C2" s="3" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D2" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E2" s="3" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B2" s="3" t="s">
+      <x:c r="F2" s="3" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C2" s="3" t="s">
+      <x:c r="G2" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D2" s="3" t="s">
+      <x:c r="H2" s="3" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E2" s="3" t="s">
+      <x:c r="I2" s="3" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F2" s="3" t="s">
+      <x:c r="J2" s="3" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G2" s="3" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H2" s="3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="I2" s="3" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J2" s="3" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K2" s="3" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L2" s="3" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M2" s="3" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="N2" s="6" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="O2" s="7"/>
-      <x:c r="P2" s="7"/>
-      <x:c r="Q2" s="7"/>
-      <x:c r="R2" s="7"/>
-      <x:c r="S2" s="7"/>
-      <x:c r="T2" s="7"/>
-      <x:c r="U2" s="7"/>
-      <x:c r="V2" s="7"/>
-      <x:c r="W2" s="7"/>
-      <x:c r="X2" s="7"/>
-      <x:c r="Y2" s="7"/>
+      <x:c r="K2" s="3"/>
+      <x:c r="L2" s="3"/>
+      <x:c r="M2" s="3"/>
+      <x:c r="N2" s="3"/>
+      <x:c r="O2" s="3"/>
+      <x:c r="P2" s="3"/>
+      <x:c r="Q2" s="3"/>
+      <x:c r="R2" s="3"/>
+      <x:c r="S2" s="3"/>
+      <x:c r="T2" s="3"/>
+      <x:c r="U2" s="3"/>
     </x:row>
     <x:row r="3" ht="20" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="I3" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="J3" s="2" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="K3" s="2" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="L3" s="2" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="M3" s="2" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="N3" s="8" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="O3" s="9"/>
-      <x:c r="P3" s="9"/>
-      <x:c r="Q3" s="9"/>
-      <x:c r="R3" s="9"/>
-      <x:c r="S3" s="9"/>
-      <x:c r="T3" s="9"/>
-      <x:c r="U3" s="9"/>
-      <x:c r="V3" s="9"/>
-      <x:c r="W3" s="9"/>
-      <x:c r="X3" s="9"/>
-      <x:c r="Y3" s="19"/>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K3" s="2"/>
+      <x:c r="L3" s="2"/>
+      <x:c r="M3" s="2"/>
+      <x:c r="N3" s="2"/>
+      <x:c r="O3" s="2"/>
+      <x:c r="P3" s="2"/>
+      <x:c r="Q3" s="2"/>
+      <x:c r="R3" s="2"/>
+      <x:c r="S3" s="2"/>
+      <x:c r="T3" s="2"/>
+      <x:c r="U3" s="2"/>
     </x:row>
     <x:row r="4" ht="20" customHeight="1">
       <x:c r="A4" s="2" t="s">
@@ -1592,40 +1491,36 @@
       <x:c r="G4" s="2"/>
       <x:c r="H4" s="2"/>
       <x:c r="I4" s="2"/>
-      <x:c r="J4" s="2"/>
-      <x:c r="K4" s="2"/>
+      <x:c r="J4" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="K4" s="2" t="s">
+        <x:v>28</x:v>
+      </x:c>
       <x:c r="L4" s="2"/>
       <x:c r="M4" s="2"/>
-      <x:c r="N4" s="5" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="O4" s="5" t="str">
-        <x:v>*collisionShapes</x:v>
-      </x:c>
-      <x:c r="P4" s="5"/>
-      <x:c r="Q4" s="5"/>
-      <x:c r="R4" s="5"/>
-      <x:c r="S4" s="5" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="T4" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="U4" s="5" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="V4" s="12" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="W4" s="13"/>
-      <x:c r="X4" s="14"/>
-      <x:c r="Y4" s="5" t="s">
-        <x:v>39</x:v>
+      <x:c r="N4" s="2"/>
+      <x:c r="O4" s="2" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="P4" s="2" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q4" s="2" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="R4" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="S4" s="2"/>
+      <x:c r="T4" s="2"/>
+      <x:c r="U4" s="2" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="20" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B5" s="3"/>
       <x:c r="C5" s="3"/>
@@ -1635,35 +1530,31 @@
       <x:c r="G5" s="3"/>
       <x:c r="H5" s="3"/>
       <x:c r="I5" s="3"/>
-      <x:c r="J5" s="3"/>
-      <x:c r="K5" s="3"/>
+      <x:c r="J5" s="3" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K5" s="3" t="s">
+        <x:v>35</x:v>
+      </x:c>
       <x:c r="L5" s="3"/>
       <x:c r="M5" s="3"/>
-      <x:c r="N5" s="10" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="O5" s="10" t="str">
-        <x:v>碰撞形状列表</x:v>
-      </x:c>
-      <x:c r="P5" s="10"/>
-      <x:c r="Q5" s="10"/>
-      <x:c r="R5" s="10"/>
-      <x:c r="S5" s="10" t="s">
+      <x:c r="N5" s="3"/>
+      <x:c r="O5" s="3" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="P5" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="Q5" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="R5" s="3" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="S5" s="3"/>
+      <x:c r="T5" s="3"/>
+      <x:c r="U5" s="3" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="T5" s="10" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="U5" s="10" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="V5" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="W5" s="16"/>
-      <x:c r="X5" s="17"/>
-      <x:c r="Y5" s="10" t="s">
-        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20" customHeight="1">
@@ -1679,35 +1570,31 @@
       <x:c r="H6" s="2"/>
       <x:c r="I6" s="2"/>
       <x:c r="J6" s="2"/>
-      <x:c r="K6" s="2"/>
-      <x:c r="L6" s="2"/>
-      <x:c r="M6" s="2"/>
-      <x:c r="N6" s="5"/>
-      <x:c r="O6" s="5" t="s">
+      <x:c r="K6" s="2" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="L6" s="2" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="M6" s="2" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="N6" s="2" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="P6" s="5" t="s">
+      <x:c r="O6" s="2"/>
+      <x:c r="P6" s="2"/>
+      <x:c r="Q6" s="2"/>
+      <x:c r="R6" s="2" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="Q6" s="5" t="s">
+      <x:c r="S6" s="2" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="R6" s="5" t="s">
+      <x:c r="T6" s="2" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="S6" s="5"/>
-      <x:c r="T6" s="5"/>
-      <x:c r="U6" s="5"/>
-      <x:c r="V6" s="5" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="W6" s="5" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="X6" s="5" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="Y6" s="5"/>
+      <x:c r="U6" s="2"/>
     </x:row>
     <x:row r="7" ht="20" customHeight="1">
       <x:c r="A7" s="4"/>
@@ -1715,62 +1602,58 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D7" s="5" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E7" s="5">
+        <x:v>1.61</x:v>
+      </x:c>
+      <x:c r="F7" s="4" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G7" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H7" s="5">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I7" s="4">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J7" s="4" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="D7" s="4">
+      <x:c r="K7" s="4" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L7" s="4"/>
+      <x:c r="M7" s="4" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N7" s="4" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="O7" s="4">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E7" s="4" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="F7" s="4" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G7" s="4" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="H7" s="4">
+      <x:c r="P7" s="4">
         <x:v>187.5</x:v>
       </x:c>
-      <x:c r="I7" s="4">
-        <x:v>1.61</x:v>
-      </x:c>
-      <x:c r="J7" s="4" t="s">
+      <x:c r="Q7" s="4"/>
+      <x:c r="R7" s="4">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S7" s="4" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="K7" s="4">
+      <x:c r="T7" s="4">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="U7" s="4" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L7" s="4">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="M7" s="4">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="N7" s="11" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="O7" s="11" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P7" s="11"/>
-      <x:c r="Q7" s="11" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="R7" s="11" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="S7" s="11">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="T7" s="11">
-        <x:v>187.5</x:v>
-      </x:c>
-      <x:c r="U7" s="11"/>
-      <x:c r="V7" s="11"/>
-      <x:c r="W7" s="11"/>
-      <x:c r="X7" s="11"/>
-      <x:c r="Y7" s="11"/>
     </x:row>
     <x:row r="8" ht="20" customHeight="1">
       <x:c r="A8" s="4"/>
@@ -1778,62 +1661,58 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C8" s="4" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D8" s="4">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D8" s="5" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E8" s="5">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="F8" s="4" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G8" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H8" s="5">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I8" s="4">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J8" s="4" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K8" s="4" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L8" s="4"/>
+      <x:c r="M8" s="4" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N8" s="4" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="O8" s="4">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E8" s="4" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F8" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G8" s="4" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H8" s="4">
+      <x:c r="P8" s="4">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="I8" s="4">
-        <x:v>1.2</x:v>
-      </x:c>
-      <x:c r="J8" s="4" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="K8" s="4">
+      <x:c r="Q8" s="4"/>
+      <x:c r="R8" s="4">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S8" s="4" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="T8" s="4">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="U8" s="4" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L8" s="4">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="M8" s="4">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="N8" s="11" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O8" s="11" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P8" s="11"/>
-      <x:c r="Q8" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="R8" s="11" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="S8" s="11">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="T8" s="11">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="U8" s="11"/>
-      <x:c r="V8" s="11"/>
-      <x:c r="W8" s="11"/>
-      <x:c r="X8" s="11"/>
-      <x:c r="Y8" s="11"/>
     </x:row>
     <x:row r="9" ht="20" customHeight="1">
       <x:c r="A9" s="4"/>
@@ -1841,62 +1720,58 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D9" s="4">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="E9" s="4" t="s">
+      <x:c r="D9" s="5" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E9" s="5">
+        <x:v>1.96</x:v>
+      </x:c>
+      <x:c r="F9" s="4" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G9" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H9" s="5">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I9" s="4">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J9" s="4" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="F9" s="4" t="s">
+      <x:c r="K9" s="4" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L9" s="4"/>
+      <x:c r="M9" s="4" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="G9" s="4" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H9" s="4">
+      <x:c r="N9" s="4" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="O9" s="4">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="P9" s="4">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="I9" s="4">
-        <x:v>1.96</x:v>
-      </x:c>
-      <x:c r="J9" s="4" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="K9" s="4">
+      <x:c r="Q9" s="4"/>
+      <x:c r="R9" s="4">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S9" s="4" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="T9" s="4">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="U9" s="4" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L9" s="4">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="M9" s="4">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="N9" s="11" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="O9" s="11" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P9" s="11"/>
-      <x:c r="Q9" s="11" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="R9" s="11" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="S9" s="11">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="T9" s="11">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="U9" s="11"/>
-      <x:c r="V9" s="11"/>
-      <x:c r="W9" s="11"/>
-      <x:c r="X9" s="11"/>
-      <x:c r="Y9" s="11"/>
     </x:row>
     <x:row r="10" ht="17.25" customHeight="1">
       <x:c r="A10" s="4"/>
@@ -1904,62 +1779,58 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D10" s="5" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E10" s="5">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="F10" s="4" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G10" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H10" s="5">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="I10" s="4">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J10" s="4" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D10" s="4">
+      <x:c r="K10" s="4" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L10" s="4"/>
+      <x:c r="M10" s="4" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="N10" s="4" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="O10" s="4">
         <x:v>1600</x:v>
       </x:c>
-      <x:c r="E10" s="4" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F10" s="4" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G10" s="4" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H10" s="4">
+      <x:c r="P10" s="4">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="I10" s="4">
-        <x:v>1.4</x:v>
-      </x:c>
-      <x:c r="J10" s="4" t="s">
+      <x:c r="Q10" s="4"/>
+      <x:c r="R10" s="4">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S10" s="4" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="K10" s="4">
+      <x:c r="T10" s="4">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="U10" s="4" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L10" s="4">
-        <x:v>1000</x:v>
-      </x:c>
-      <x:c r="M10" s="4">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N10" s="11" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="O10" s="11" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P10" s="11"/>
-      <x:c r="Q10" s="11" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="R10" s="11" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="S10" s="11">
-        <x:v>1600</x:v>
-      </x:c>
-      <x:c r="T10" s="11">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="U10" s="11"/>
-      <x:c r="V10" s="11"/>
-      <x:c r="W10" s="11"/>
-      <x:c r="X10" s="11"/>
-      <x:c r="Y10" s="11"/>
     </x:row>
     <x:row r="11" ht="17.25" customHeight="1">
       <x:c r="A11" s="4"/>
@@ -1967,718 +1838,955 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D11" s="5" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E11" s="5">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="F11" s="4" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G11" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H11" s="5">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="I11" s="4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J11" s="4" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="D11" s="4" t="n">
-        <x:v>6000</x:v>
-      </x:c>
-      <x:c r="E11" s="4" t="s">
+      <x:c r="K11" s="4" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L11" s="4"/>
+      <x:c r="M11" s="4" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="F11" s="4" t="s">
+      <x:c r="N11" s="10" t="str">
+        <x:v>0.5,0.31</x:v>
+      </x:c>
+      <x:c r="O11" s="4" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="P11" s="4">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="Q11" s="7"/>
+      <x:c r="R11" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S11" s="4" t="str">
+        <x:v>0,40</x:v>
+      </x:c>
+      <x:c r="T11" s="4" t="n">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="U11" s="4" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="16.5">
+      <x:c r="A12" s="5"/>
+      <x:c r="B12" s="5"/>
+      <x:c r="C12" s="5"/>
+      <x:c r="D12" s="5"/>
+      <x:c r="E12" s="5"/>
+      <x:c r="F12" s="5"/>
+      <x:c r="G12" s="5"/>
+      <x:c r="H12" s="5"/>
+      <x:c r="I12" s="5"/>
+      <x:c r="J12" s="5"/>
+      <x:c r="K12" s="5" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L12" s="5"/>
+      <x:c r="M12" s="5" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G11" s="4" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H11" s="4">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="I11" s="4">
-        <x:v>1.4</x:v>
-      </x:c>
-      <x:c r="J11" s="4" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="K11" s="4">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L11" s="4">
-        <x:v>3000</x:v>
-      </x:c>
-      <x:c r="M11" s="4">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N11" s="11" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="O11" s="11" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P11" s="11"/>
-      <x:c r="Q11" s="28" t="str">
-        <x:v>90,180</x:v>
-      </x:c>
-      <x:c r="R11" s="28" t="str">
-        <x:v>0.5,0.305556</x:v>
-      </x:c>
-      <x:c r="S11" s="11" t="n">
-        <x:v>6000</x:v>
-      </x:c>
-      <x:c r="T11" s="11">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="U11" s="11"/>
-      <x:c r="V11" s="11"/>
-      <x:c r="W11" s="11"/>
-      <x:c r="X11" s="11"/>
-      <x:c r="Y11" s="11"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="26"/>
-      <x:c r="B12" s="26"/>
-      <x:c r="C12" s="26"/>
-      <x:c r="D12" s="26"/>
-      <x:c r="E12" s="26"/>
-      <x:c r="F12" s="26"/>
-      <x:c r="G12" s="26"/>
-      <x:c r="H12" s="26"/>
-      <x:c r="I12" s="26"/>
-      <x:c r="J12" s="26"/>
-      <x:c r="K12" s="26"/>
-      <x:c r="L12" s="26"/>
-      <x:c r="M12" s="26"/>
-      <x:c r="N12" s="26"/>
-      <x:c r="O12" s="26" t="str">
-        <x:v>矩形</x:v>
-      </x:c>
-      <x:c r="P12" s="26"/>
-      <x:c r="Q12" s="29" t="str">
-        <x:v>105,90</x:v>
-      </x:c>
-      <x:c r="R12" s="29" t="str">
-        <x:v>1.5,-0.111111</x:v>
-      </x:c>
-      <x:c r="S12" s="26"/>
-      <x:c r="T12" s="26"/>
-      <x:c r="U12" s="26"/>
-      <x:c r="V12" s="26"/>
-      <x:c r="W12" s="27"/>
-      <x:c r="X12" s="26"/>
-      <x:c r="Y12" s="26"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="26"/>
-      <x:c r="B13" s="26"/>
-      <x:c r="C13" s="26"/>
-      <x:c r="D13" s="26"/>
-      <x:c r="E13" s="26"/>
-      <x:c r="F13" s="26"/>
-      <x:c r="G13" s="26"/>
-      <x:c r="H13" s="26"/>
-      <x:c r="I13" s="26"/>
-      <x:c r="J13" s="26"/>
-      <x:c r="K13" s="26"/>
-      <x:c r="L13" s="26"/>
-      <x:c r="M13" s="26"/>
-      <x:c r="N13" s="26"/>
-      <x:c r="O13" s="26" t="str">
-        <x:v>矩形</x:v>
-      </x:c>
-      <x:c r="P13" s="26"/>
-      <x:c r="Q13" s="29" t="str">
-        <x:v>105,90</x:v>
-      </x:c>
-      <x:c r="R13" s="29" t="str">
-        <x:v>-0.5,-0.111111</x:v>
-      </x:c>
-      <x:c r="S13" s="26"/>
-      <x:c r="T13" s="26"/>
-      <x:c r="U13" s="26"/>
-      <x:c r="V13" s="26"/>
-      <x:c r="W13" s="27"/>
-      <x:c r="X13" s="26"/>
-      <x:c r="Y13" s="26"/>
+      <x:c r="N12" s="11" t="str">
+        <x:v>1.5,-0.11</x:v>
+      </x:c>
+      <x:c r="O12" s="5"/>
+      <x:c r="P12" s="5"/>
+      <x:c r="Q12" s="8"/>
+      <x:c r="R12" s="8" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="S12" s="5" t="str">
+        <x:v>-85,0</x:v>
+      </x:c>
+      <x:c r="T12" s="5" t="n">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="U12" s="5"/>
+    </x:row>
+    <x:row r="13" ht="16.5">
+      <x:c r="A13" s="6"/>
+      <x:c r="B13" s="6"/>
+      <x:c r="C13" s="5"/>
+      <x:c r="D13" s="5"/>
+      <x:c r="E13" s="5"/>
+      <x:c r="F13" s="5"/>
+      <x:c r="G13" s="5"/>
+      <x:c r="H13" s="5"/>
+      <x:c r="I13" s="5"/>
+      <x:c r="J13" s="6"/>
+      <x:c r="K13" s="6" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L13" s="6"/>
+      <x:c r="M13" s="6" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="N13" s="12" t="str">
+        <x:v>-0.5,-0.11</x:v>
+      </x:c>
+      <x:c r="O13" s="6"/>
+      <x:c r="P13" s="6"/>
+      <x:c r="Q13" s="9"/>
+      <x:c r="R13" s="9" t="n">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="S13" s="6" t="str">
+        <x:v>80,-20</x:v>
+      </x:c>
+      <x:c r="T13" s="6" t="n">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="U13" s="6"/>
     </x:row>
     <x:row r="14">
-      <x:c r="W14" s="18"/>
+      <x:c r="A14" s="17"/>
+      <x:c r="B14" s="17"/>
+      <x:c r="C14" s="17"/>
+      <x:c r="D14" s="17"/>
+      <x:c r="E14" s="17"/>
+      <x:c r="F14" s="17"/>
+      <x:c r="G14" s="17"/>
+      <x:c r="H14" s="17"/>
+      <x:c r="I14" s="17"/>
+      <x:c r="J14" s="17"/>
+      <x:c r="K14" s="17"/>
+      <x:c r="L14" s="17"/>
+      <x:c r="M14" s="17"/>
+      <x:c r="N14" s="17"/>
+      <x:c r="O14" s="17"/>
+      <x:c r="P14" s="17"/>
+      <x:c r="Q14" s="17"/>
+      <x:c r="R14" s="17" t="n">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="S14" s="18" t="str">
+        <x:v>-45,-90</x:v>
+      </x:c>
+      <x:c r="T14" s="17" t="n">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="U14" s="17"/>
     </x:row>
     <x:row r="15">
-      <x:c r="W15" s="18"/>
+      <x:c r="A15" s="17"/>
+      <x:c r="B15" s="17"/>
+      <x:c r="C15" s="17"/>
+      <x:c r="D15" s="17"/>
+      <x:c r="E15" s="17"/>
+      <x:c r="F15" s="17"/>
+      <x:c r="G15" s="17"/>
+      <x:c r="H15" s="17"/>
+      <x:c r="I15" s="17"/>
+      <x:c r="J15" s="17"/>
+      <x:c r="K15" s="17"/>
+      <x:c r="L15" s="17"/>
+      <x:c r="M15" s="17"/>
+      <x:c r="N15" s="17"/>
+      <x:c r="O15" s="17"/>
+      <x:c r="P15" s="17"/>
+      <x:c r="Q15" s="17"/>
+      <x:c r="R15" s="17" t="n">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="S15" s="18" t="str">
+        <x:v>55,-110</x:v>
+      </x:c>
+      <x:c r="T15" s="17" t="n">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="U15" s="17"/>
     </x:row>
     <x:row r="16">
-      <x:c r="W16" s="18"/>
+      <x:c r="Q16"/>
+      <x:c r="R16"/>
     </x:row>
     <x:row r="17">
-      <x:c r="W17" s="18"/>
+      <x:c r="Q17"/>
+      <x:c r="R17"/>
     </x:row>
     <x:row r="18">
-      <x:c r="W18" s="18"/>
+      <x:c r="Q18"/>
+      <x:c r="R18"/>
     </x:row>
     <x:row r="19">
-      <x:c r="W19" s="18"/>
+      <x:c r="Q19"/>
+      <x:c r="R19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="W20" s="18"/>
+      <x:c r="Q20"/>
+      <x:c r="R20"/>
     </x:row>
     <x:row r="21">
-      <x:c r="W21" s="18"/>
+      <x:c r="Q21"/>
+      <x:c r="R21"/>
     </x:row>
     <x:row r="22">
-      <x:c r="W22" s="18"/>
+      <x:c r="Q22"/>
+      <x:c r="R22"/>
     </x:row>
     <x:row r="23">
-      <x:c r="W23" s="18"/>
+      <x:c r="Q23"/>
+      <x:c r="R23"/>
     </x:row>
     <x:row r="24">
-      <x:c r="W24" s="18"/>
+      <x:c r="Q24"/>
+      <x:c r="R24"/>
     </x:row>
     <x:row r="25">
-      <x:c r="W25" s="18"/>
+      <x:c r="Q25"/>
+      <x:c r="R25"/>
     </x:row>
     <x:row r="26">
-      <x:c r="W26" s="18"/>
+      <x:c r="Q26"/>
+      <x:c r="R26"/>
     </x:row>
     <x:row r="27">
-      <x:c r="W27" s="18"/>
+      <x:c r="Q27"/>
+      <x:c r="R27"/>
     </x:row>
     <x:row r="28">
-      <x:c r="W28" s="18"/>
+      <x:c r="Q28"/>
+      <x:c r="R28"/>
     </x:row>
     <x:row r="29">
-      <x:c r="W29" s="18"/>
+      <x:c r="Q29"/>
+      <x:c r="R29"/>
     </x:row>
     <x:row r="30">
-      <x:c r="W30" s="18"/>
+      <x:c r="Q30"/>
+      <x:c r="R30"/>
     </x:row>
     <x:row r="31">
-      <x:c r="W31" s="18"/>
+      <x:c r="Q31"/>
+      <x:c r="R31"/>
     </x:row>
     <x:row r="32">
-      <x:c r="W32" s="18"/>
+      <x:c r="Q32"/>
+      <x:c r="R32"/>
     </x:row>
     <x:row r="33">
-      <x:c r="W33" s="18"/>
+      <x:c r="Q33"/>
+      <x:c r="R33"/>
     </x:row>
     <x:row r="34">
-      <x:c r="W34" s="18"/>
+      <x:c r="Q34"/>
+      <x:c r="R34"/>
     </x:row>
     <x:row r="35">
-      <x:c r="W35" s="18"/>
+      <x:c r="Q35"/>
+      <x:c r="R35"/>
     </x:row>
     <x:row r="36">
-      <x:c r="W36" s="18"/>
+      <x:c r="Q36"/>
+      <x:c r="R36"/>
     </x:row>
     <x:row r="37">
-      <x:c r="W37" s="18"/>
+      <x:c r="Q37"/>
+      <x:c r="R37"/>
     </x:row>
     <x:row r="38">
-      <x:c r="W38" s="18"/>
+      <x:c r="Q38"/>
+      <x:c r="R38"/>
     </x:row>
     <x:row r="39">
-      <x:c r="W39" s="18"/>
+      <x:c r="Q39"/>
+      <x:c r="R39"/>
     </x:row>
     <x:row r="40">
-      <x:c r="W40" s="18"/>
+      <x:c r="Q40"/>
+      <x:c r="R40"/>
     </x:row>
     <x:row r="41">
-      <x:c r="W41" s="18"/>
+      <x:c r="Q41"/>
+      <x:c r="R41"/>
     </x:row>
     <x:row r="42">
-      <x:c r="W42" s="18"/>
+      <x:c r="Q42"/>
+      <x:c r="R42"/>
     </x:row>
     <x:row r="43">
-      <x:c r="W43" s="18"/>
+      <x:c r="Q43"/>
+      <x:c r="R43"/>
     </x:row>
     <x:row r="44">
-      <x:c r="W44" s="18"/>
+      <x:c r="Q44"/>
+      <x:c r="R44"/>
     </x:row>
     <x:row r="45">
-      <x:c r="W45" s="18"/>
+      <x:c r="Q45"/>
+      <x:c r="R45"/>
     </x:row>
     <x:row r="46">
-      <x:c r="W46" s="18"/>
+      <x:c r="Q46"/>
+      <x:c r="R46"/>
     </x:row>
     <x:row r="47">
-      <x:c r="W47" s="18"/>
+      <x:c r="Q47"/>
+      <x:c r="R47"/>
     </x:row>
     <x:row r="48">
-      <x:c r="W48" s="18"/>
+      <x:c r="Q48"/>
+      <x:c r="R48"/>
     </x:row>
     <x:row r="49">
-      <x:c r="W49" s="18"/>
+      <x:c r="Q49"/>
+      <x:c r="R49"/>
     </x:row>
     <x:row r="50">
-      <x:c r="W50" s="18"/>
+      <x:c r="Q50"/>
+      <x:c r="R50"/>
     </x:row>
     <x:row r="51">
-      <x:c r="W51" s="18"/>
+      <x:c r="Q51"/>
+      <x:c r="R51"/>
     </x:row>
     <x:row r="52">
-      <x:c r="W52" s="18"/>
+      <x:c r="Q52"/>
+      <x:c r="R52"/>
     </x:row>
     <x:row r="53">
-      <x:c r="W53" s="18"/>
+      <x:c r="Q53"/>
+      <x:c r="R53"/>
     </x:row>
     <x:row r="54">
-      <x:c r="W54" s="18"/>
+      <x:c r="Q54"/>
+      <x:c r="R54"/>
     </x:row>
     <x:row r="55">
-      <x:c r="W55" s="18"/>
+      <x:c r="Q55"/>
+      <x:c r="R55"/>
     </x:row>
     <x:row r="56">
-      <x:c r="W56" s="18"/>
+      <x:c r="Q56"/>
+      <x:c r="R56"/>
     </x:row>
     <x:row r="57">
-      <x:c r="W57" s="18"/>
+      <x:c r="Q57"/>
+      <x:c r="R57"/>
     </x:row>
     <x:row r="58">
-      <x:c r="W58" s="18"/>
+      <x:c r="Q58"/>
+      <x:c r="R58"/>
     </x:row>
     <x:row r="59">
-      <x:c r="W59" s="18"/>
+      <x:c r="Q59"/>
+      <x:c r="R59"/>
     </x:row>
     <x:row r="60">
-      <x:c r="W60" s="18"/>
+      <x:c r="Q60"/>
+      <x:c r="R60"/>
     </x:row>
     <x:row r="61">
-      <x:c r="W61" s="18"/>
+      <x:c r="Q61"/>
+      <x:c r="R61"/>
     </x:row>
     <x:row r="62">
-      <x:c r="W62" s="18"/>
+      <x:c r="Q62"/>
+      <x:c r="R62"/>
     </x:row>
     <x:row r="63">
-      <x:c r="W63" s="18"/>
+      <x:c r="Q63"/>
+      <x:c r="R63"/>
     </x:row>
     <x:row r="64">
-      <x:c r="W64" s="18"/>
+      <x:c r="Q64"/>
+      <x:c r="R64"/>
     </x:row>
     <x:row r="65">
-      <x:c r="W65" s="18"/>
+      <x:c r="Q65"/>
+      <x:c r="R65"/>
     </x:row>
     <x:row r="66">
-      <x:c r="W66" s="18"/>
+      <x:c r="Q66"/>
+      <x:c r="R66"/>
     </x:row>
     <x:row r="67">
-      <x:c r="W67" s="18"/>
+      <x:c r="Q67"/>
+      <x:c r="R67"/>
     </x:row>
     <x:row r="68">
-      <x:c r="W68" s="18"/>
+      <x:c r="Q68"/>
+      <x:c r="R68"/>
     </x:row>
     <x:row r="69">
-      <x:c r="W69" s="18"/>
+      <x:c r="Q69"/>
+      <x:c r="R69"/>
     </x:row>
     <x:row r="70">
-      <x:c r="W70" s="18"/>
+      <x:c r="Q70"/>
+      <x:c r="R70"/>
     </x:row>
     <x:row r="71">
-      <x:c r="W71" s="18"/>
+      <x:c r="Q71"/>
+      <x:c r="R71"/>
     </x:row>
     <x:row r="72">
-      <x:c r="W72" s="18"/>
+      <x:c r="Q72"/>
+      <x:c r="R72"/>
     </x:row>
     <x:row r="73">
-      <x:c r="W73" s="18"/>
+      <x:c r="Q73"/>
+      <x:c r="R73"/>
     </x:row>
     <x:row r="74">
-      <x:c r="W74" s="18"/>
+      <x:c r="Q74"/>
+      <x:c r="R74"/>
     </x:row>
     <x:row r="75">
-      <x:c r="W75" s="18"/>
+      <x:c r="Q75"/>
+      <x:c r="R75"/>
     </x:row>
     <x:row r="76">
-      <x:c r="W76" s="18"/>
+      <x:c r="Q76"/>
+      <x:c r="R76"/>
     </x:row>
     <x:row r="77">
-      <x:c r="W77" s="18"/>
+      <x:c r="Q77"/>
+      <x:c r="R77"/>
     </x:row>
     <x:row r="78">
-      <x:c r="W78" s="18"/>
+      <x:c r="Q78"/>
+      <x:c r="R78"/>
     </x:row>
     <x:row r="79">
-      <x:c r="W79" s="18"/>
+      <x:c r="Q79"/>
+      <x:c r="R79"/>
     </x:row>
     <x:row r="80">
-      <x:c r="W80" s="18"/>
+      <x:c r="Q80"/>
+      <x:c r="R80"/>
     </x:row>
     <x:row r="81">
-      <x:c r="W81" s="18"/>
+      <x:c r="Q81"/>
+      <x:c r="R81"/>
     </x:row>
     <x:row r="82">
-      <x:c r="W82" s="18"/>
+      <x:c r="Q82"/>
+      <x:c r="R82"/>
     </x:row>
     <x:row r="83">
-      <x:c r="W83" s="18"/>
+      <x:c r="Q83"/>
+      <x:c r="R83"/>
     </x:row>
     <x:row r="84">
-      <x:c r="W84" s="18"/>
+      <x:c r="Q84"/>
+      <x:c r="R84"/>
     </x:row>
     <x:row r="85">
-      <x:c r="W85" s="18"/>
+      <x:c r="Q85"/>
+      <x:c r="R85"/>
     </x:row>
     <x:row r="86">
-      <x:c r="W86" s="18"/>
+      <x:c r="Q86"/>
+      <x:c r="R86"/>
     </x:row>
     <x:row r="87">
-      <x:c r="W87" s="18"/>
+      <x:c r="Q87"/>
+      <x:c r="R87"/>
     </x:row>
     <x:row r="88">
-      <x:c r="W88" s="18"/>
+      <x:c r="Q88"/>
+      <x:c r="R88"/>
     </x:row>
     <x:row r="89">
-      <x:c r="W89" s="18"/>
+      <x:c r="Q89"/>
+      <x:c r="R89"/>
     </x:row>
     <x:row r="90">
-      <x:c r="W90" s="18"/>
+      <x:c r="Q90"/>
+      <x:c r="R90"/>
     </x:row>
     <x:row r="91">
-      <x:c r="W91" s="18"/>
+      <x:c r="Q91"/>
+      <x:c r="R91"/>
     </x:row>
     <x:row r="92">
-      <x:c r="W92" s="18"/>
+      <x:c r="Q92"/>
+      <x:c r="R92"/>
     </x:row>
     <x:row r="93">
-      <x:c r="W93" s="18"/>
+      <x:c r="Q93"/>
+      <x:c r="R93"/>
     </x:row>
     <x:row r="94">
-      <x:c r="W94" s="18"/>
+      <x:c r="Q94"/>
+      <x:c r="R94"/>
     </x:row>
     <x:row r="95">
-      <x:c r="W95" s="18"/>
+      <x:c r="Q95"/>
+      <x:c r="R95"/>
     </x:row>
     <x:row r="96">
-      <x:c r="W96" s="18"/>
+      <x:c r="Q96"/>
+      <x:c r="R96"/>
     </x:row>
     <x:row r="97">
-      <x:c r="W97" s="18"/>
+      <x:c r="Q97"/>
+      <x:c r="R97"/>
     </x:row>
     <x:row r="98">
-      <x:c r="W98" s="18"/>
+      <x:c r="Q98"/>
+      <x:c r="R98"/>
     </x:row>
     <x:row r="99">
-      <x:c r="W99" s="18"/>
+      <x:c r="Q99"/>
+      <x:c r="R99"/>
     </x:row>
     <x:row r="100">
-      <x:c r="W100" s="18"/>
+      <x:c r="Q100"/>
+      <x:c r="R100"/>
     </x:row>
     <x:row r="101">
-      <x:c r="W101" s="18"/>
+      <x:c r="Q101"/>
+      <x:c r="R101"/>
     </x:row>
     <x:row r="102">
-      <x:c r="W102" s="18"/>
+      <x:c r="Q102"/>
+      <x:c r="R102"/>
     </x:row>
     <x:row r="103">
-      <x:c r="W103" s="18"/>
+      <x:c r="Q103"/>
+      <x:c r="R103"/>
     </x:row>
     <x:row r="104">
-      <x:c r="W104" s="18"/>
+      <x:c r="Q104"/>
+      <x:c r="R104"/>
     </x:row>
     <x:row r="105">
-      <x:c r="W105" s="18"/>
+      <x:c r="Q105"/>
+      <x:c r="R105"/>
     </x:row>
     <x:row r="106">
-      <x:c r="W106" s="18"/>
+      <x:c r="Q106"/>
+      <x:c r="R106"/>
     </x:row>
     <x:row r="107">
-      <x:c r="W107" s="18"/>
+      <x:c r="Q107"/>
+      <x:c r="R107"/>
     </x:row>
     <x:row r="108">
-      <x:c r="W108" s="18"/>
+      <x:c r="Q108"/>
+      <x:c r="R108"/>
     </x:row>
     <x:row r="109">
-      <x:c r="W109" s="18"/>
+      <x:c r="Q109"/>
+      <x:c r="R109"/>
     </x:row>
     <x:row r="110">
-      <x:c r="W110" s="18"/>
+      <x:c r="Q110"/>
+      <x:c r="R110"/>
     </x:row>
     <x:row r="111">
-      <x:c r="W111" s="18"/>
+      <x:c r="Q111"/>
+      <x:c r="R111"/>
     </x:row>
     <x:row r="112">
-      <x:c r="W112" s="18"/>
+      <x:c r="Q112"/>
+      <x:c r="R112"/>
     </x:row>
     <x:row r="113">
-      <x:c r="W113" s="18"/>
+      <x:c r="Q113"/>
+      <x:c r="R113"/>
     </x:row>
     <x:row r="114">
-      <x:c r="W114" s="18"/>
+      <x:c r="Q114"/>
+      <x:c r="R114"/>
     </x:row>
     <x:row r="115">
-      <x:c r="W115" s="18"/>
+      <x:c r="Q115"/>
+      <x:c r="R115"/>
     </x:row>
     <x:row r="116">
-      <x:c r="W116" s="18"/>
+      <x:c r="Q116"/>
+      <x:c r="R116"/>
     </x:row>
     <x:row r="117">
-      <x:c r="W117" s="18"/>
+      <x:c r="Q117"/>
+      <x:c r="R117"/>
     </x:row>
     <x:row r="118">
-      <x:c r="W118" s="18"/>
+      <x:c r="Q118"/>
+      <x:c r="R118"/>
     </x:row>
     <x:row r="119">
-      <x:c r="W119" s="18"/>
+      <x:c r="Q119"/>
+      <x:c r="R119"/>
     </x:row>
     <x:row r="120">
-      <x:c r="W120" s="18"/>
+      <x:c r="Q120"/>
+      <x:c r="R120"/>
     </x:row>
     <x:row r="121">
-      <x:c r="W121" s="18"/>
+      <x:c r="Q121"/>
+      <x:c r="R121"/>
     </x:row>
     <x:row r="122">
-      <x:c r="W122" s="18"/>
+      <x:c r="Q122"/>
+      <x:c r="R122"/>
     </x:row>
     <x:row r="123">
-      <x:c r="W123" s="18"/>
+      <x:c r="Q123"/>
+      <x:c r="R123"/>
     </x:row>
     <x:row r="124">
-      <x:c r="W124" s="18"/>
+      <x:c r="Q124"/>
+      <x:c r="R124"/>
     </x:row>
     <x:row r="125">
-      <x:c r="W125" s="18"/>
+      <x:c r="Q125"/>
+      <x:c r="R125"/>
     </x:row>
     <x:row r="126">
-      <x:c r="W126" s="18"/>
+      <x:c r="Q126"/>
+      <x:c r="R126"/>
     </x:row>
     <x:row r="127">
-      <x:c r="W127" s="18"/>
+      <x:c r="Q127"/>
+      <x:c r="R127"/>
     </x:row>
     <x:row r="128">
-      <x:c r="W128" s="18"/>
+      <x:c r="Q128"/>
+      <x:c r="R128"/>
     </x:row>
     <x:row r="129">
-      <x:c r="W129" s="18"/>
+      <x:c r="Q129"/>
+      <x:c r="R129"/>
     </x:row>
     <x:row r="130">
-      <x:c r="W130" s="18"/>
+      <x:c r="Q130"/>
+      <x:c r="R130"/>
     </x:row>
     <x:row r="131">
-      <x:c r="W131" s="18"/>
+      <x:c r="Q131"/>
+      <x:c r="R131"/>
     </x:row>
     <x:row r="132">
-      <x:c r="W132" s="18"/>
+      <x:c r="Q132"/>
+      <x:c r="R132"/>
     </x:row>
     <x:row r="133">
-      <x:c r="W133" s="18"/>
+      <x:c r="Q133"/>
+      <x:c r="R133"/>
     </x:row>
     <x:row r="134">
-      <x:c r="W134" s="18"/>
+      <x:c r="Q134"/>
+      <x:c r="R134"/>
     </x:row>
     <x:row r="135">
-      <x:c r="W135" s="18"/>
+      <x:c r="Q135"/>
+      <x:c r="R135"/>
     </x:row>
     <x:row r="136">
-      <x:c r="W136" s="18"/>
+      <x:c r="Q136"/>
+      <x:c r="R136"/>
     </x:row>
     <x:row r="137">
-      <x:c r="W137" s="18"/>
+      <x:c r="Q137"/>
+      <x:c r="R137"/>
     </x:row>
     <x:row r="138">
-      <x:c r="W138" s="18"/>
+      <x:c r="Q138"/>
+      <x:c r="R138"/>
     </x:row>
     <x:row r="139">
-      <x:c r="W139" s="18"/>
+      <x:c r="Q139"/>
+      <x:c r="R139"/>
     </x:row>
     <x:row r="140">
-      <x:c r="W140" s="18"/>
+      <x:c r="Q140"/>
+      <x:c r="R140"/>
     </x:row>
     <x:row r="141">
-      <x:c r="W141" s="18"/>
+      <x:c r="Q141"/>
+      <x:c r="R141"/>
     </x:row>
     <x:row r="142">
-      <x:c r="W142" s="18"/>
+      <x:c r="Q142"/>
+      <x:c r="R142"/>
     </x:row>
     <x:row r="143">
-      <x:c r="W143" s="18"/>
+      <x:c r="Q143"/>
+      <x:c r="R143"/>
     </x:row>
     <x:row r="144">
-      <x:c r="W144" s="18"/>
+      <x:c r="Q144"/>
+      <x:c r="R144"/>
     </x:row>
     <x:row r="145">
-      <x:c r="W145" s="18"/>
+      <x:c r="Q145"/>
+      <x:c r="R145"/>
     </x:row>
     <x:row r="146">
-      <x:c r="W146" s="18"/>
+      <x:c r="Q146"/>
+      <x:c r="R146"/>
     </x:row>
     <x:row r="147">
-      <x:c r="W147" s="18"/>
+      <x:c r="Q147"/>
+      <x:c r="R147"/>
     </x:row>
     <x:row r="148">
-      <x:c r="W148" s="18"/>
+      <x:c r="Q148"/>
+      <x:c r="R148"/>
     </x:row>
     <x:row r="149">
-      <x:c r="W149" s="18"/>
+      <x:c r="Q149"/>
+      <x:c r="R149"/>
     </x:row>
     <x:row r="150">
-      <x:c r="W150" s="18"/>
+      <x:c r="Q150"/>
+      <x:c r="R150"/>
     </x:row>
     <x:row r="151">
-      <x:c r="W151" s="18"/>
+      <x:c r="Q151"/>
+      <x:c r="R151"/>
     </x:row>
     <x:row r="152">
-      <x:c r="W152" s="18"/>
+      <x:c r="Q152"/>
+      <x:c r="R152"/>
     </x:row>
     <x:row r="153">
-      <x:c r="W153" s="18"/>
+      <x:c r="Q153"/>
+      <x:c r="R153"/>
     </x:row>
     <x:row r="154">
-      <x:c r="W154" s="18"/>
+      <x:c r="Q154"/>
+      <x:c r="R154"/>
     </x:row>
     <x:row r="155">
-      <x:c r="W155" s="18"/>
+      <x:c r="Q155"/>
+      <x:c r="R155"/>
     </x:row>
     <x:row r="156">
-      <x:c r="W156" s="18"/>
+      <x:c r="Q156"/>
+      <x:c r="R156"/>
     </x:row>
     <x:row r="157">
-      <x:c r="W157" s="18"/>
+      <x:c r="Q157"/>
+      <x:c r="R157"/>
     </x:row>
     <x:row r="158">
-      <x:c r="W158" s="18"/>
+      <x:c r="Q158"/>
+      <x:c r="R158"/>
     </x:row>
     <x:row r="159">
-      <x:c r="W159" s="18"/>
+      <x:c r="Q159"/>
+      <x:c r="R159"/>
     </x:row>
     <x:row r="160">
-      <x:c r="W160" s="18"/>
+      <x:c r="Q160"/>
+      <x:c r="R160"/>
     </x:row>
     <x:row r="161">
-      <x:c r="W161" s="18"/>
+      <x:c r="Q161"/>
+      <x:c r="R161"/>
     </x:row>
     <x:row r="162">
-      <x:c r="W162" s="18"/>
+      <x:c r="Q162"/>
+      <x:c r="R162"/>
     </x:row>
     <x:row r="163">
-      <x:c r="W163" s="18"/>
+      <x:c r="Q163"/>
+      <x:c r="R163"/>
     </x:row>
     <x:row r="164">
-      <x:c r="W164" s="18"/>
+      <x:c r="Q164"/>
+      <x:c r="R164"/>
     </x:row>
     <x:row r="165">
-      <x:c r="W165" s="18"/>
+      <x:c r="Q165"/>
+      <x:c r="R165"/>
     </x:row>
     <x:row r="166">
-      <x:c r="W166" s="18"/>
+      <x:c r="Q166"/>
+      <x:c r="R166"/>
     </x:row>
     <x:row r="167">
-      <x:c r="W167" s="18"/>
+      <x:c r="Q167"/>
+      <x:c r="R167"/>
     </x:row>
     <x:row r="168">
-      <x:c r="W168" s="18"/>
+      <x:c r="Q168"/>
+      <x:c r="R168"/>
     </x:row>
     <x:row r="169">
-      <x:c r="W169" s="18"/>
+      <x:c r="Q169"/>
+      <x:c r="R169"/>
     </x:row>
     <x:row r="170">
-      <x:c r="W170" s="18"/>
+      <x:c r="Q170"/>
+      <x:c r="R170"/>
     </x:row>
     <x:row r="171">
-      <x:c r="W171" s="18"/>
+      <x:c r="Q171"/>
+      <x:c r="R171"/>
     </x:row>
     <x:row r="172">
-      <x:c r="W172" s="18"/>
+      <x:c r="Q172"/>
+      <x:c r="R172"/>
     </x:row>
     <x:row r="173">
-      <x:c r="W173" s="18"/>
+      <x:c r="Q173"/>
+      <x:c r="R173"/>
     </x:row>
     <x:row r="174">
-      <x:c r="W174" s="18"/>
+      <x:c r="Q174"/>
+      <x:c r="R174"/>
     </x:row>
     <x:row r="175">
-      <x:c r="W175" s="18"/>
+      <x:c r="Q175"/>
+      <x:c r="R175"/>
     </x:row>
     <x:row r="176">
-      <x:c r="W176" s="18"/>
+      <x:c r="Q176"/>
+      <x:c r="R176"/>
     </x:row>
     <x:row r="177">
-      <x:c r="W177" s="18"/>
+      <x:c r="Q177"/>
+      <x:c r="R177"/>
     </x:row>
     <x:row r="178">
-      <x:c r="W178" s="18"/>
+      <x:c r="Q178"/>
+      <x:c r="R178"/>
     </x:row>
     <x:row r="179">
-      <x:c r="W179" s="18"/>
+      <x:c r="Q179"/>
+      <x:c r="R179"/>
     </x:row>
     <x:row r="180">
-      <x:c r="W180" s="18"/>
+      <x:c r="Q180"/>
+      <x:c r="R180"/>
     </x:row>
     <x:row r="181">
-      <x:c r="W181" s="18"/>
+      <x:c r="Q181"/>
+      <x:c r="R181"/>
     </x:row>
     <x:row r="182">
-      <x:c r="W182" s="18"/>
+      <x:c r="Q182"/>
+      <x:c r="R182"/>
     </x:row>
     <x:row r="183">
-      <x:c r="W183" s="18"/>
+      <x:c r="Q183"/>
+      <x:c r="R183"/>
     </x:row>
     <x:row r="184">
-      <x:c r="W184" s="18"/>
+      <x:c r="Q184"/>
+      <x:c r="R184"/>
     </x:row>
     <x:row r="185">
-      <x:c r="W185" s="18"/>
+      <x:c r="Q185"/>
+      <x:c r="R185"/>
     </x:row>
     <x:row r="186">
-      <x:c r="W186" s="18"/>
+      <x:c r="Q186"/>
+      <x:c r="R186"/>
     </x:row>
     <x:row r="187">
-      <x:c r="W187" s="18"/>
+      <x:c r="Q187"/>
+      <x:c r="R187"/>
     </x:row>
     <x:row r="188">
-      <x:c r="W188" s="18"/>
+      <x:c r="Q188"/>
+      <x:c r="R188"/>
     </x:row>
     <x:row r="189">
-      <x:c r="W189" s="18"/>
+      <x:c r="Q189"/>
+      <x:c r="R189"/>
     </x:row>
     <x:row r="190">
-      <x:c r="W190" s="18"/>
+      <x:c r="Q190"/>
+      <x:c r="R190"/>
     </x:row>
     <x:row r="191">
-      <x:c r="W191" s="18"/>
+      <x:c r="Q191"/>
+      <x:c r="R191"/>
     </x:row>
     <x:row r="192">
-      <x:c r="W192" s="18"/>
+      <x:c r="Q192"/>
+      <x:c r="R192"/>
     </x:row>
     <x:row r="193">
-      <x:c r="W193" s="18"/>
+      <x:c r="Q193"/>
+      <x:c r="R193"/>
     </x:row>
     <x:row r="194">
-      <x:c r="W194" s="18"/>
+      <x:c r="Q194"/>
+      <x:c r="R194"/>
     </x:row>
     <x:row r="195">
-      <x:c r="W195" s="18"/>
+      <x:c r="Q195"/>
+      <x:c r="R195"/>
     </x:row>
     <x:row r="196">
-      <x:c r="W196" s="18"/>
+      <x:c r="Q196"/>
+      <x:c r="R196"/>
     </x:row>
     <x:row r="197">
-      <x:c r="W197" s="18"/>
+      <x:c r="Q197"/>
+      <x:c r="R197"/>
     </x:row>
     <x:row r="198">
-      <x:c r="W198" s="18"/>
+      <x:c r="Q198"/>
+      <x:c r="R198"/>
     </x:row>
     <x:row r="199">
-      <x:c r="W199" s="18"/>
+      <x:c r="Q199"/>
+      <x:c r="R199"/>
     </x:row>
     <x:row r="200">
-      <x:c r="W200" s="18"/>
+      <x:c r="Q200"/>
+      <x:c r="R200"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="N1:Y1"/>
-    <x:mergeCell ref="N2:Y2"/>
-    <x:mergeCell ref="N3:Y3"/>
-    <x:mergeCell ref="O4:R4"/>
-    <x:mergeCell ref="V4:X4"/>
-    <x:mergeCell ref="O5:R5"/>
-    <x:mergeCell ref="V5:X5"/>
+    <x:mergeCell ref="J1:U1"/>
+    <x:mergeCell ref="J2:U2"/>
+    <x:mergeCell ref="J3:U3"/>
+    <x:mergeCell ref="K4:N4"/>
+    <x:mergeCell ref="R4:T4"/>
+    <x:mergeCell ref="K5:N5"/>
+    <x:mergeCell ref="R5:T5"/>
   </x:mergeCells>
   <x:dataValidations count="5">
     <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C1048576">
       <x:formula1>"普通,精英,Boss"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="J4:J1048576">
+    <x:dataValidation type="custom" sqref="D1:D200 E1:E200 G1:G200 H1:H200">
+      <x:formula1>TRUE</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="F4:F1048576 J4:J1048576">
       <x:formula1>"单发,双发,散射,瞄准"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="O7:O1048576">
+    <x:dataValidation type="list" sqref="K7:K1048576 O7:O1048576">
       <x:formula1>"圆形,矩形"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="Y7:Y200">
+    <x:dataValidation type="list" sqref="U7:U200 Y7:Y200">
       <x:formula1>"true,false"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="O12:O13">
-      <x:formula1>"圆形,矩形"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95bfd185889245be"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R043d1436e4c94b2f"/>
 </x:worksheet>
 </file>
--- a/RaidenDemo/文档/配置表/EnemyResource.xlsx
+++ b/RaidenDemo/文档/配置表/EnemyResource.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc691c75d6bb943c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4fee7cb85e834c7c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -226,9 +226,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">aircraft/enemy/battleEliteInterceptor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">150,130</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Boss</x:t>
@@ -1806,11 +1803,11 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="L10" s="4"/>
-      <x:c r="M10" s="4" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="N10" s="4" t="s">
-        <x:v>54</x:v>
+      <x:c r="M10" s="4" t="str">
+        <x:v>150,50</x:v>
+      </x:c>
+      <x:c r="N10" s="4" t="str">
+        <x:v>0.5,0.14</x:v>
       </x:c>
       <x:c r="O10" s="4">
         <x:v>1600</x:v>
@@ -1838,10 +1835,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D11" s="5" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="D11" s="5" t="s">
-        <x:v>69</x:v>
       </x:c>
       <x:c r="E11" s="5">
         <x:v>1.4</x:v>
@@ -1859,14 +1856,14 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="4" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="K11" s="4" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="L11" s="4"/>
       <x:c r="M11" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="N11" s="10" t="str">
         <x:v>0.5,0.31</x:v>
@@ -1907,7 +1904,7 @@
       </x:c>
       <x:c r="L12" s="5"/>
       <x:c r="M12" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="N12" s="11" t="str">
         <x:v>1.5,-0.11</x:v>
@@ -1942,7 +1939,7 @@
       </x:c>
       <x:c r="L13" s="6"/>
       <x:c r="M13" s="6" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="N13" s="12" t="str">
         <x:v>-0.5,-0.11</x:v>
@@ -2787,6 +2784,6 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R043d1436e4c94b2f"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce4fec56c76d48c4"/>
 </x:worksheet>
 </file>
--- a/RaidenDemo/文档/配置表/EnemyResource.xlsx
+++ b/RaidenDemo/文档/配置表/EnemyResource.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="90">
   <si>
     <t>##var</t>
   </si>
@@ -246,6 +246,15 @@
   </si>
   <si>
     <t>0,-81</t>
+  </si>
+  <si>
+    <t>-45,25</t>
+  </si>
+  <si>
+    <t>40,-10</t>
+  </si>
+  <si>
+    <t>-20,-45</t>
   </si>
   <si>
     <t>Boss</t>
@@ -671,7 +680,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -731,6 +740,17 @@
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -870,7 +890,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
@@ -882,13 +902,13 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
@@ -897,19 +917,19 @@
     <xf numFmtId="0" fontId="15" fillId="6" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="10">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="11">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="11">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="12">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
@@ -995,7 +1015,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1"/>
@@ -1013,23 +1033,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1503,7 +1530,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z201"/>
+  <dimension ref="A1:Z204"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="8" style="1" customWidth="1"/>
@@ -1571,7 +1598,7 @@
       <c r="W1" s="4"/>
       <c r="X1" s="4"/>
       <c r="Y1" s="4"/>
-      <c r="Z1" s="11"/>
+      <c r="Z1" s="13"/>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:26">
       <c r="A2" s="5" t="s">
@@ -1613,7 +1640,7 @@
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
-      <c r="Z2" s="11"/>
+      <c r="Z2" s="13"/>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:26">
       <c r="A3" s="3" t="s">
@@ -1655,7 +1682,7 @@
       <c r="W3" s="4"/>
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
-      <c r="Z3" s="11"/>
+      <c r="Z3" s="13"/>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:26">
       <c r="A4" s="3" t="s">
@@ -1674,7 +1701,7 @@
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
-      <c r="K4" s="11"/>
+      <c r="K4" s="13"/>
       <c r="L4" s="3" t="s">
         <v>21</v>
       </c>
@@ -1691,12 +1718,12 @@
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
-      <c r="V4" s="11"/>
+      <c r="V4" s="13"/>
       <c r="W4" s="3" t="s">
         <v>24</v>
       </c>
       <c r="X4" s="4"/>
-      <c r="Y4" s="11"/>
+      <c r="Y4" s="13"/>
       <c r="Z4" s="3" t="s">
         <v>25</v>
       </c>
@@ -1718,7 +1745,7 @@
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
-      <c r="K5" s="11"/>
+      <c r="K5" s="13"/>
       <c r="L5" s="5" t="s">
         <v>28</v>
       </c>
@@ -1735,12 +1762,12 @@
       <c r="S5" s="4"/>
       <c r="T5" s="4"/>
       <c r="U5" s="4"/>
-      <c r="V5" s="11"/>
+      <c r="V5" s="13"/>
       <c r="W5" s="5" t="s">
         <v>31</v>
       </c>
       <c r="X5" s="4"/>
-      <c r="Y5" s="11"/>
+      <c r="Y5" s="13"/>
       <c r="Z5" s="5" t="s">
         <v>32</v>
       </c>
@@ -1922,10 +1949,10 @@
       <c r="N8" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="O8" s="10">
+      <c r="O8" s="11">
         <v>11001</v>
       </c>
-      <c r="P8" s="10">
+      <c r="P8" s="11">
         <v>1</v>
       </c>
       <c r="Q8" s="6">
@@ -1952,7 +1979,7 @@
       <c r="X8" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="Y8" s="10">
+      <c r="Y8" s="11">
         <v>5001</v>
       </c>
       <c r="Z8" s="6" t="b">
@@ -1976,10 +2003,10 @@
       <c r="N9" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="O9" s="10">
+      <c r="O9" s="11">
         <v>11001</v>
       </c>
-      <c r="P9" s="10">
+      <c r="P9" s="11">
         <v>1</v>
       </c>
       <c r="Q9" s="6">
@@ -2044,10 +2071,10 @@
       <c r="N10" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="O10" s="10">
+      <c r="O10" s="11">
         <v>11001</v>
       </c>
-      <c r="P10" s="10">
+      <c r="P10" s="11">
         <v>1</v>
       </c>
       <c r="Q10" s="6">
@@ -2074,7 +2101,7 @@
       <c r="X10" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="Y10" s="10">
+      <c r="Y10" s="11">
         <v>5001</v>
       </c>
       <c r="Z10" s="6" t="b">
@@ -2112,7 +2139,7 @@
         <v>71</v>
       </c>
       <c r="L11" s="6">
-        <v>1600</v>
+        <v>1000</v>
       </c>
       <c r="M11" s="6">
         <v>90</v>
@@ -2120,10 +2147,10 @@
       <c r="N11" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="O11" s="10">
+      <c r="O11" s="6">
         <v>11001</v>
       </c>
-      <c r="P11" s="10">
+      <c r="P11" s="6">
         <v>1</v>
       </c>
       <c r="Q11" s="6">
@@ -2148,9 +2175,9 @@
         <v>0</v>
       </c>
       <c r="X11" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y11" s="10">
+        <v>73</v>
+      </c>
+      <c r="Y11" s="6">
         <v>5001</v>
       </c>
       <c r="Z11" s="6" t="b">
@@ -2159,275 +2186,363 @@
     </row>
     <row r="12" ht="16.5" customHeight="1" spans="1:26">
       <c r="A12" s="6"/>
-      <c r="B12" s="6">
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="9"/>
+      <c r="U12" s="9"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="6">
+        <v>120</v>
+      </c>
+      <c r="X12" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y12" s="6">
+        <v>5001</v>
+      </c>
+      <c r="Z12" s="9"/>
+    </row>
+    <row r="13" ht="16.5" customHeight="1" spans="1:26">
+      <c r="A13" s="6"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="6">
+        <v>240</v>
+      </c>
+      <c r="X13" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>5001</v>
+      </c>
+      <c r="Z13" s="9"/>
+    </row>
+    <row r="14" ht="16.5" customHeight="1" spans="1:26">
+      <c r="A14" s="6"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="8"/>
+      <c r="V14" s="8"/>
+      <c r="W14" s="6">
+        <v>750</v>
+      </c>
+      <c r="X14" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y14" s="6">
+        <v>5101</v>
+      </c>
+      <c r="Z14" s="8"/>
+    </row>
+    <row r="15" ht="16.5" spans="1:26">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6">
         <v>5</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E12" s="7">
+      <c r="C15" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="7">
         <v>3000</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F15" s="6">
         <v>1</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="H12" s="6" t="s">
+      <c r="G15" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K12" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="L12" s="6">
-        <v>10000</v>
-      </c>
-      <c r="M12" s="6">
+      <c r="I15" s="6"/>
+      <c r="J15" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L15" s="6">
+        <v>2000</v>
+      </c>
+      <c r="M15" s="6">
         <v>70</v>
       </c>
-      <c r="N12" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="O12" s="10">
+      <c r="N15" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="O15" s="11">
         <v>11001</v>
       </c>
-      <c r="P12" s="10">
+      <c r="P15" s="11">
         <v>1</v>
       </c>
-      <c r="Q12" s="12">
+      <c r="Q15" s="14">
         <v>5</v>
       </c>
-      <c r="R12" s="12">
+      <c r="R15" s="14">
         <v>1190</v>
       </c>
-      <c r="S12" s="12">
+      <c r="S15" s="14">
         <v>0</v>
       </c>
-      <c r="T12" s="12">
+      <c r="T15" s="14">
         <v>-90</v>
       </c>
-      <c r="U12" s="12" t="s">
+      <c r="U15" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="V12" s="12">
+      <c r="V15" s="14">
         <v>57</v>
       </c>
-      <c r="W12" s="12">
+      <c r="W15" s="14">
         <v>0</v>
       </c>
-      <c r="X12" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y12" s="10">
-        <v>5001</v>
-      </c>
-      <c r="Z12" s="6" t="b">
+      <c r="X15" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y15" s="11">
+        <v>5101</v>
+      </c>
+      <c r="Z15" s="6" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" spans="1:26">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7" t="s">
+    <row r="16" ht="16.5" spans="1:26">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13"/>
-      <c r="R13" s="13"/>
-      <c r="S13" s="13"/>
-      <c r="T13" s="13"/>
-      <c r="U13" s="13"/>
-      <c r="V13" s="13"/>
-      <c r="W13" s="13">
-        <v>140</v>
-      </c>
-      <c r="X13" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y13" s="10">
-        <v>5001</v>
-      </c>
-      <c r="Z13" s="7"/>
-    </row>
-    <row r="14" ht="16.5" spans="1:26">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9" t="s">
+      <c r="I16" s="7"/>
+      <c r="J16" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="15"/>
+      <c r="R16" s="15"/>
+      <c r="S16" s="15"/>
+      <c r="T16" s="15"/>
+      <c r="U16" s="15"/>
+      <c r="V16" s="15"/>
+      <c r="W16" s="15">
+        <v>150</v>
+      </c>
+      <c r="X16" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y16" s="11">
+        <v>5101</v>
+      </c>
+      <c r="Z16" s="7"/>
+    </row>
+    <row r="17" ht="16.5" spans="1:26">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="K14" s="14" t="s">
+      <c r="I17" s="10"/>
+      <c r="J17" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="14"/>
-      <c r="T14" s="14"/>
-      <c r="U14" s="14"/>
-      <c r="V14" s="14"/>
-      <c r="W14" s="14">
-        <v>280</v>
-      </c>
-      <c r="X14" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y14" s="10">
-        <v>5001</v>
-      </c>
-      <c r="Z14" s="9"/>
-    </row>
-    <row r="15" spans="1:26">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
-      <c r="U15" s="10"/>
-      <c r="V15" s="10"/>
-      <c r="W15" s="10">
-        <v>420</v>
-      </c>
-      <c r="X15" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="Y15" s="10">
-        <v>5001</v>
-      </c>
-      <c r="Z15" s="10"/>
-    </row>
-    <row r="16" spans="1:26">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="10"/>
-      <c r="S16" s="10"/>
-      <c r="T16" s="10"/>
-      <c r="U16" s="10"/>
-      <c r="V16" s="10"/>
-      <c r="W16" s="10">
-        <v>560</v>
-      </c>
-      <c r="X16" s="15" t="s">
+      <c r="K17" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="Y16" s="10">
-        <v>5001</v>
-      </c>
-      <c r="Z16" s="10"/>
-    </row>
-    <row r="17" spans="14:23">
-      <c r="N17"/>
-      <c r="O17"/>
-      <c r="P17"/>
-      <c r="Q17"/>
-      <c r="R17"/>
-      <c r="S17"/>
-      <c r="T17"/>
-      <c r="U17"/>
-      <c r="V17"/>
-      <c r="W17"/>
-    </row>
-    <row r="18" spans="14:23">
-      <c r="N18"/>
-      <c r="O18"/>
-      <c r="P18"/>
-      <c r="Q18"/>
-      <c r="R18"/>
-      <c r="S18"/>
-      <c r="T18"/>
-      <c r="U18"/>
-      <c r="V18"/>
-      <c r="W18"/>
-    </row>
-    <row r="19" spans="14:23">
-      <c r="N19"/>
-      <c r="O19"/>
-      <c r="P19"/>
-      <c r="Q19"/>
-      <c r="R19"/>
-      <c r="S19"/>
-      <c r="T19"/>
-      <c r="U19"/>
-      <c r="V19"/>
-      <c r="W19"/>
-    </row>
-    <row r="20" spans="14:23">
-      <c r="N20"/>
-      <c r="O20"/>
-      <c r="P20"/>
-      <c r="Q20"/>
-      <c r="R20"/>
-      <c r="S20"/>
-      <c r="T20"/>
-      <c r="U20"/>
-      <c r="V20"/>
-      <c r="W20"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="16"/>
+      <c r="S17" s="16"/>
+      <c r="T17" s="16"/>
+      <c r="U17" s="16"/>
+      <c r="V17" s="16"/>
+      <c r="W17" s="16">
+        <v>300</v>
+      </c>
+      <c r="X17" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y17" s="11">
+        <v>5101</v>
+      </c>
+      <c r="Z17" s="10"/>
+    </row>
+    <row r="18" spans="1:26">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="11"/>
+      <c r="T18" s="11"/>
+      <c r="U18" s="11"/>
+      <c r="V18" s="11"/>
+      <c r="W18" s="11">
+        <v>450</v>
+      </c>
+      <c r="X18" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y18" s="11">
+        <v>5101</v>
+      </c>
+      <c r="Z18" s="11"/>
+    </row>
+    <row r="19" spans="1:26">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="11"/>
+      <c r="T19" s="11"/>
+      <c r="U19" s="11"/>
+      <c r="V19" s="11"/>
+      <c r="W19" s="11">
+        <v>600</v>
+      </c>
+      <c r="X19" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y19" s="11">
+        <v>5101</v>
+      </c>
+      <c r="Z19" s="11"/>
+    </row>
+    <row r="20" ht="16.5" spans="1:26">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="12"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="12"/>
+      <c r="U20" s="12"/>
+      <c r="V20" s="12"/>
+      <c r="W20" s="18">
+        <v>1100</v>
+      </c>
+      <c r="X20" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y20" s="18">
+        <v>5301</v>
+      </c>
+      <c r="Z20" s="12"/>
     </row>
     <row r="21" spans="14:23">
       <c r="N21"/>
@@ -4601,8 +4716,44 @@
       <c r="V201"/>
       <c r="W201"/>
     </row>
+    <row r="202" spans="14:23">
+      <c r="N202"/>
+      <c r="O202"/>
+      <c r="P202"/>
+      <c r="Q202"/>
+      <c r="R202"/>
+      <c r="S202"/>
+      <c r="T202"/>
+      <c r="U202"/>
+      <c r="V202"/>
+      <c r="W202"/>
+    </row>
+    <row r="203" spans="14:23">
+      <c r="N203"/>
+      <c r="O203"/>
+      <c r="P203"/>
+      <c r="Q203"/>
+      <c r="R203"/>
+      <c r="S203"/>
+      <c r="T203"/>
+      <c r="U203"/>
+      <c r="V203"/>
+      <c r="W203"/>
+    </row>
+    <row r="204" spans="14:23">
+      <c r="N204"/>
+      <c r="O204"/>
+      <c r="P204"/>
+      <c r="Q204"/>
+      <c r="R204"/>
+      <c r="S204"/>
+      <c r="T204"/>
+      <c r="U204"/>
+      <c r="V204"/>
+      <c r="W204"/>
+    </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="47">
     <mergeCell ref="G1:Z1"/>
     <mergeCell ref="G2:Z2"/>
     <mergeCell ref="G3:Z3"/>
@@ -4613,21 +4764,43 @@
     <mergeCell ref="N5:V5"/>
     <mergeCell ref="W5:Y5"/>
     <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B11:B14"/>
     <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C11:C14"/>
     <mergeCell ref="D8:D9"/>
+    <mergeCell ref="D11:D14"/>
     <mergeCell ref="E8:E9"/>
+    <mergeCell ref="E11:E14"/>
     <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F11:F14"/>
     <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G11:G14"/>
     <mergeCell ref="H8:H9"/>
+    <mergeCell ref="H11:H14"/>
     <mergeCell ref="I8:I9"/>
+    <mergeCell ref="I11:I14"/>
     <mergeCell ref="J8:J9"/>
+    <mergeCell ref="J11:J14"/>
     <mergeCell ref="K8:K9"/>
+    <mergeCell ref="K11:K14"/>
     <mergeCell ref="L8:L9"/>
+    <mergeCell ref="L11:L14"/>
     <mergeCell ref="M8:M9"/>
+    <mergeCell ref="M11:M14"/>
+    <mergeCell ref="N11:N14"/>
+    <mergeCell ref="O11:O14"/>
+    <mergeCell ref="P11:P14"/>
+    <mergeCell ref="Q11:Q14"/>
+    <mergeCell ref="R11:R14"/>
+    <mergeCell ref="S11:S14"/>
+    <mergeCell ref="T11:T14"/>
+    <mergeCell ref="U11:U14"/>
+    <mergeCell ref="V11:V14"/>
     <mergeCell ref="W8:W9"/>
     <mergeCell ref="X8:X9"/>
     <mergeCell ref="Y8:Y9"/>
     <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="Z11:Z14"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" sqref="C7:C1048576">
